--- a/front/public/templates/plantilla_carga_masiva.xlsx
+++ b/front/public/templates/plantilla_carga_masiva.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Carga Masiva" sheetId="1" r:id="rId1"/>
+    <sheet name="Actas" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -64,9 +64,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -398,303 +397,179 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q6"/>
-  <cols>
-    <col min="1" max="1" width="15.83203125" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="15.83203125" customWidth="1"/>
-    <col min="9" max="9" width="25.83203125" customWidth="1"/>
-    <col min="10" max="10" width="15.83203125" customWidth="1"/>
-    <col min="11" max="11" width="15.83203125" customWidth="1"/>
-    <col min="12" max="12" width="15.83203125" customWidth="1"/>
-    <col min="13" max="13" width="15.83203125" customWidth="1"/>
-    <col min="14" max="14" width="18.83203125" customWidth="1"/>
-    <col min="15" max="15" width="25.83203125" customWidth="1"/>
-    <col min="16" max="16" width="35.83203125" customWidth="1"/>
-    <col min="17" max="17" width="25.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:R3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>tipo_acta</v>
+      </c>
+      <c r="B1" t="str">
+        <v>cui</v>
+      </c>
+      <c r="C1" t="str">
+        <v>libro</v>
+      </c>
+      <c r="D1" t="str">
+        <v>numero_acta</v>
+      </c>
+      <c r="E1" t="str">
+        <v>anio</v>
+      </c>
+      <c r="F1" t="str">
+        <v>fecha_acta</v>
+      </c>
+      <c r="G1" t="str">
+        <v>dni</v>
+      </c>
+      <c r="H1" t="str">
         <v>tipo_documento</v>
       </c>
-      <c r="B1" s="1" t="str">
-        <v>dni</v>
-      </c>
-      <c r="C1" t="str">
+      <c r="I1" t="str">
         <v>nombres</v>
       </c>
-      <c r="D1" t="str">
+      <c r="J1" t="str">
         <v>apellido_paterno</v>
       </c>
-      <c r="E1" t="str">
+      <c r="K1" t="str">
         <v>apellido_materno</v>
       </c>
-      <c r="F1" t="str">
+      <c r="L1" t="str">
         <v>sexo</v>
       </c>
-      <c r="G1" t="str">
+      <c r="M1" t="str">
         <v>fecha_nacimiento</v>
       </c>
-      <c r="H1" s="1" t="str">
+      <c r="N1" t="str">
         <v>telefono</v>
-      </c>
-      <c r="I1" t="str">
-        <v>persona_observaciones</v>
-      </c>
-      <c r="J1" t="str">
-        <v>tipo_acta</v>
-      </c>
-      <c r="K1" s="1" t="str">
-        <v>libro</v>
-      </c>
-      <c r="L1" s="1" t="str">
-        <v>numero_acta</v>
-      </c>
-      <c r="M1" s="1" t="str">
-        <v>anio</v>
-      </c>
-      <c r="N1" t="str">
-        <v>fecha_acta</v>
       </c>
       <c r="O1" t="str">
         <v>acta_observaciones</v>
       </c>
       <c r="P1" t="str">
-        <v>carpeta_ruta</v>
+        <v>persona_observaciones</v>
       </c>
       <c r="Q1" t="str">
         <v>nombre_archivo_pdf</v>
+      </c>
+      <c r="R1" t="str">
+        <v>carpeta_ruta</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>NACIMIENTO</v>
+      </c>
+      <c r="B2" t="str">
+        <v>12345678</v>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2">
+        <v>2024</v>
+      </c>
+      <c r="F2" t="str">
+        <v>2024-03-11</v>
+      </c>
+      <c r="G2" t="str">
+        <v>12345678</v>
+      </c>
+      <c r="H2" t="str">
         <v>DNI</v>
       </c>
-      <c r="B2" s="1" t="str">
-        <v>70654321</v>
-      </c>
-      <c r="C2" t="str">
+      <c r="I2" t="str">
         <v>JUAN ALBERTO</v>
       </c>
-      <c r="D2" t="str">
+      <c r="J2" t="str">
         <v>PEREZ</v>
       </c>
-      <c r="E2" t="str">
+      <c r="K2" t="str">
         <v>GARCIA</v>
       </c>
-      <c r="F2" t="str">
+      <c r="L2" t="str">
         <v>M</v>
       </c>
-      <c r="G2" t="str">
-        <v>1990-05-15</v>
-      </c>
-      <c r="H2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="I2" t="str">
-        <v/>
-      </c>
-      <c r="J2" t="str">
-        <v>NACIMIENTO</v>
-      </c>
-      <c r="K2" s="1" t="str">
-        <v>1</v>
-      </c>
-      <c r="L2" s="1" t="str">
-        <v>45</v>
-      </c>
-      <c r="M2" s="1" t="str">
-        <v>1990</v>
+      <c r="M2" t="str">
+        <v>2024-01-01</v>
       </c>
       <c r="N2" t="str">
-        <v>1990-06-20</v>
+        <v>987654321</v>
       </c>
       <c r="O2" t="str">
-        <v/>
+        <v>Registro masivo CUI</v>
       </c>
       <c r="P2" t="str">
-        <v>prueba/matrimonios/LIBRO 1</v>
+        <v/>
       </c>
       <c r="Q2" t="str">
-        <v>Documento 1.pdf</v>
+        <v>ejemplo_cui.pdf</v>
+      </c>
+      <c r="R2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>NACIMIENTO</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v>45</v>
+      </c>
+      <c r="D3" t="str">
+        <v>123</v>
+      </c>
+      <c r="E3">
+        <v>1995</v>
+      </c>
+      <c r="F3" t="str">
+        <v>1995-05-20</v>
+      </c>
+      <c r="G3" t="str">
+        <v>87654321</v>
+      </c>
+      <c r="H3" t="str">
         <v>DNI</v>
       </c>
-      <c r="B3" s="1" t="str">
-        <v>10203040</v>
-      </c>
-      <c r="C3" t="str">
+      <c r="I3" t="str">
         <v>MARIA ELENA</v>
       </c>
-      <c r="D3" t="str">
-        <v>LOPEZ</v>
-      </c>
-      <c r="E3" t="str">
+      <c r="J3" t="str">
         <v>ROJAS</v>
       </c>
-      <c r="F3" t="str">
+      <c r="K3" t="str">
+        <v>VILCA</v>
+      </c>
+      <c r="L3" t="str">
         <v>F</v>
       </c>
-      <c r="G3" t="str">
-        <v>1985-10-25</v>
-      </c>
-      <c r="H3" s="1" t="str">
-        <v>987654321</v>
-      </c>
-      <c r="I3" t="str">
-        <v/>
-      </c>
-      <c r="J3" t="str">
-        <v>MATRIMONIO</v>
-      </c>
-      <c r="K3" s="1" t="str">
-        <v>2</v>
-      </c>
-      <c r="L3" s="1" t="str">
-        <v>128</v>
-      </c>
-      <c r="M3" s="1" t="str">
-        <v>2010</v>
+      <c r="M3" t="str">
+        <v>1995-05-15</v>
       </c>
       <c r="N3" t="str">
-        <v>2010-12-15</v>
+        <v/>
       </c>
       <c r="O3" t="str">
-        <v>Union antigua</v>
+        <v>Registro masivo Clásico</v>
       </c>
       <c r="P3" t="str">
-        <v>prueba/matrimonios/LIBRO 1</v>
+        <v/>
       </c>
       <c r="Q3" t="str">
-        <v>Documento 2.pdf</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>DNI</v>
-      </c>
-      <c r="B4" s="1" t="str">
-        <v>30405060</v>
-      </c>
-      <c r="C4" t="str">
-        <v>PEDRO PABLO</v>
-      </c>
-      <c r="D4" t="str">
-        <v>VILLANUEVA</v>
-      </c>
-      <c r="E4" t="str">
-        <v>CASTRO</v>
-      </c>
-      <c r="F4" t="str">
-        <v>M</v>
-      </c>
-      <c r="G4" t="str">
-        <v>1950-01-01</v>
-      </c>
-      <c r="H4" s="1" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>Fallecido</v>
-      </c>
-      <c r="J4" t="str">
-        <v>DEFUNCION</v>
-      </c>
-      <c r="K4" s="1" t="str">
-        <v>10</v>
-      </c>
-      <c r="L4" s="1" t="str">
-        <v>77</v>
-      </c>
-      <c r="M4" s="1" t="str">
-        <v>2023</v>
-      </c>
-      <c r="N4" t="str">
-        <v>2023-11-20</v>
-      </c>
-      <c r="O4" t="str">
-        <v/>
-      </c>
-      <c r="P4" t="str">
-        <v>prueba/defunciones/LIBRO 1</v>
-      </c>
-      <c r="Q4" t="str">
-        <v>Documento 1.pdf</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>P. NACIMIENTO</v>
-      </c>
-      <c r="B5" s="1" t="str">
-        <v/>
-      </c>
-      <c r="C5" t="str">
-        <v>BEBE REGISTRADO</v>
-      </c>
-      <c r="D5" t="str">
-        <v>CUEVA</v>
-      </c>
-      <c r="E5" t="str">
-        <v>SOTO</v>
-      </c>
-      <c r="F5" t="str">
-        <v>M</v>
-      </c>
-      <c r="G5" t="str">
-        <v>2024-02-10</v>
-      </c>
-      <c r="H5" s="1" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>Sin DNI por ser menor</v>
-      </c>
-      <c r="J5" t="str">
-        <v>NACIMIENTO</v>
-      </c>
-      <c r="K5" s="1" t="str">
-        <v>5</v>
-      </c>
-      <c r="L5" s="1" t="str">
-        <v>200</v>
-      </c>
-      <c r="M5" s="1" t="str">
-        <v>2024</v>
-      </c>
-      <c r="N5" t="str">
-        <v>2024-02-28</v>
-      </c>
-      <c r="O5" t="str">
-        <v/>
-      </c>
-      <c r="P5" t="str">
-        <v>prueba/nacimientos/LIBRO 2</v>
-      </c>
-      <c r="Q5" t="str">
-        <v>Documento 1.pdf</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>INSTRUCCIONES: Azul=Ciudadano | Verde=Acta | Amarillo=Archivo PDF (opcional). Fechas en formato AAAA-MM-DD (ej: 1990-05-15). carpeta_ruta = solo la carpeta dentro del ZIP, SIN el nombre del archivo. Ej: prueba/nacimientos/LIBRO 1</v>
+        <v>ejemplo_libro.pdf</v>
+      </c>
+      <c r="R3" t="str">
+        <v>actas/1995</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:Q6"/>
-  </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/front/public/templates/plantilla_carga_masiva.xlsx
+++ b/front/public/templates/plantilla_carga_masiva.xlsx
@@ -397,7 +397,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:Y5"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="13.83203125" customWidth="1"/>
+    <col min="5" max="5" width="6.83203125" customWidth="1"/>
+    <col min="6" max="6" width="13.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+    <col min="9" max="9" width="20.83203125" customWidth="1"/>
+    <col min="10" max="10" width="18.83203125" customWidth="1"/>
+    <col min="11" max="11" width="18.83203125" customWidth="1"/>
+    <col min="12" max="12" width="6.83203125" customWidth="1"/>
+    <col min="13" max="13" width="15.83203125" customWidth="1"/>
+    <col min="14" max="14" width="13.83203125" customWidth="1"/>
+    <col min="15" max="15" width="22.83203125" customWidth="1"/>
+    <col min="16" max="16" width="16.83203125" customWidth="1"/>
+    <col min="17" max="17" width="20.83203125" customWidth="1"/>
+    <col min="18" max="18" width="20.83203125" customWidth="1"/>
+    <col min="19" max="19" width="20.83203125" customWidth="1"/>
+    <col min="20" max="20" width="20.83203125" customWidth="1"/>
+    <col min="21" max="21" width="13.83203125" customWidth="1"/>
+    <col min="22" max="22" width="22.83203125" customWidth="1"/>
+    <col min="23" max="23" width="25.83203125" customWidth="1"/>
+    <col min="24" max="24" width="20.83203125" customWidth="1"/>
+    <col min="25" max="25" width="22.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -443,16 +470,37 @@
         <v>telefono</v>
       </c>
       <c r="O1" t="str">
+        <v>persona_observaciones</v>
+      </c>
+      <c r="P1" t="str">
+        <v>conyuge_dni</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>conyuge_tipo_documento</v>
+      </c>
+      <c r="R1" t="str">
+        <v>conyuge_nombres</v>
+      </c>
+      <c r="S1" t="str">
+        <v>conyuge_apellido_paterno</v>
+      </c>
+      <c r="T1" t="str">
+        <v>conyuge_apellido_materno</v>
+      </c>
+      <c r="U1" t="str">
+        <v>conyuge_sexo</v>
+      </c>
+      <c r="V1" t="str">
+        <v>conyuge_fecha_nacimiento</v>
+      </c>
+      <c r="W1" t="str">
+        <v>nombre_archivo_pdf</v>
+      </c>
+      <c r="X1" t="str">
+        <v>carpeta_ruta</v>
+      </c>
+      <c r="Y1" t="str">
         <v>acta_observaciones</v>
-      </c>
-      <c r="P1" t="str">
-        <v>persona_observaciones</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>nombre_archivo_pdf</v>
-      </c>
-      <c r="R1" t="str">
-        <v>carpeta_ruta</v>
       </c>
     </row>
     <row r="2">
@@ -460,7 +508,7 @@
         <v>NACIMIENTO</v>
       </c>
       <c r="B2" t="str">
-        <v>12345678</v>
+        <v>20241234567890</v>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -493,21 +541,42 @@
         <v>M</v>
       </c>
       <c r="M2" t="str">
-        <v>2024-01-01</v>
+        <v>2000-05-15</v>
       </c>
       <c r="N2" t="str">
         <v>987654321</v>
       </c>
       <c r="O2" t="str">
-        <v>Registro masivo CUI</v>
+        <v/>
       </c>
       <c r="P2" t="str">
         <v/>
       </c>
       <c r="Q2" t="str">
-        <v>ejemplo_cui.pdf</v>
+        <v/>
       </c>
       <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
+      <c r="T2" t="str">
+        <v/>
+      </c>
+      <c r="U2" t="str">
+        <v/>
+      </c>
+      <c r="V2" t="str">
+        <v/>
+      </c>
+      <c r="W2" t="str">
+        <v>nacimiento_001.pdf</v>
+      </c>
+      <c r="X2" t="str">
+        <v/>
+      </c>
+      <c r="Y2" t="str">
         <v/>
       </c>
     </row>
@@ -555,21 +624,196 @@
         <v/>
       </c>
       <c r="O3" t="str">
-        <v>Registro masivo Clásico</v>
+        <v/>
       </c>
       <c r="P3" t="str">
         <v/>
       </c>
       <c r="Q3" t="str">
-        <v>ejemplo_libro.pdf</v>
+        <v/>
       </c>
       <c r="R3" t="str">
-        <v>actas/1995</v>
+        <v/>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <v/>
+      </c>
+      <c r="U3" t="str">
+        <v/>
+      </c>
+      <c r="V3" t="str">
+        <v/>
+      </c>
+      <c r="W3" t="str">
+        <v>nac_libro45_123.pdf</v>
+      </c>
+      <c r="X3" t="str">
+        <v>nacimientos/1995</v>
+      </c>
+      <c r="Y3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>MATRIMONIO</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v>12</v>
+      </c>
+      <c r="D4" t="str">
+        <v>55</v>
+      </c>
+      <c r="E4">
+        <v>2023</v>
+      </c>
+      <c r="F4" t="str">
+        <v>2023-08-20</v>
+      </c>
+      <c r="G4" t="str">
+        <v>45678901</v>
+      </c>
+      <c r="H4" t="str">
+        <v>DNI</v>
+      </c>
+      <c r="I4" t="str">
+        <v>CARLOS MIGUEL</v>
+      </c>
+      <c r="J4" t="str">
+        <v>TORRES</v>
+      </c>
+      <c r="K4" t="str">
+        <v>QUISPE</v>
+      </c>
+      <c r="L4" t="str">
+        <v>M</v>
+      </c>
+      <c r="M4" t="str">
+        <v>1990-03-10</v>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v>56789012</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>DNI</v>
+      </c>
+      <c r="R4" t="str">
+        <v>ANA LUCIA</v>
+      </c>
+      <c r="S4" t="str">
+        <v>MAMANI</v>
+      </c>
+      <c r="T4" t="str">
+        <v>FLORES</v>
+      </c>
+      <c r="U4" t="str">
+        <v>F</v>
+      </c>
+      <c r="V4" t="str">
+        <v>1992-07-22</v>
+      </c>
+      <c r="W4" t="str">
+        <v>matrimonio_55.pdf</v>
+      </c>
+      <c r="X4" t="str">
+        <v>matrimonios/2023</v>
+      </c>
+      <c r="Y4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>DEFUNCION</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v>8</v>
+      </c>
+      <c r="D5" t="str">
+        <v>201</v>
+      </c>
+      <c r="E5">
+        <v>2022</v>
+      </c>
+      <c r="F5" t="str">
+        <v>2022-11-05</v>
+      </c>
+      <c r="G5" t="str">
+        <v>11223344</v>
+      </c>
+      <c r="H5" t="str">
+        <v>DNI</v>
+      </c>
+      <c r="I5" t="str">
+        <v>PEDRO JOSE</v>
+      </c>
+      <c r="J5" t="str">
+        <v>VARGAS</v>
+      </c>
+      <c r="K5" t="str">
+        <v>HUANCA</v>
+      </c>
+      <c r="L5" t="str">
+        <v>M</v>
+      </c>
+      <c r="M5" t="str">
+        <v>1945-01-30</v>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
+        <v/>
+      </c>
+      <c r="S5" t="str">
+        <v/>
+      </c>
+      <c r="T5" t="str">
+        <v/>
+      </c>
+      <c r="U5" t="str">
+        <v/>
+      </c>
+      <c r="V5" t="str">
+        <v/>
+      </c>
+      <c r="W5" t="str">
+        <v>defuncion_201.pdf</v>
+      </c>
+      <c r="X5" t="str">
+        <v>defunciones/2022</v>
+      </c>
+      <c r="Y5" t="str">
+        <v>Fallecimiento natural</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y5"/>
   </ignoredErrors>
 </worksheet>
 </file>